--- a/cases/02_网络指标/网络指标数据.xlsx
+++ b/cases/02_网络指标/网络指标数据.xlsx
@@ -2,36 +2,183 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23837" windowHeight="11520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NR网络指标" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地理数据" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="21">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -40,12 +187,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
-        <bgColor rgb="002E75B6"/>
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -53,18 +386,311 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,7 +1043,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -427,56 +1052,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.1"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Site ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>频段</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>带宽</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>小区名称</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>上行PRB利用率</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>下行PRB利用率</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>基站数</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>5G用户数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>地区</t>
         </is>
@@ -485,30 +1114,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>北京01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>n78</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>100</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>n78-北京-01</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>65.17</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>41.25</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>22</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>9024</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
@@ -517,30 +1151,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>上海02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>n78</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>100</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>n78-上海-02</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>42.28</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>76.81999999999999</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>48</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>18870</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
@@ -549,30 +1188,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>广州03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>n78</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>100</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>n78-广州-03</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>34.78</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>61.1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>6</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>4070</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
@@ -581,30 +1225,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>深圳04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>n78</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>100</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>n78-深圳-04</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>42.03</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>65.27</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>6</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>19390</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
@@ -613,30 +1262,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>杭州05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>n78</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>100</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>n78-杭州-05</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>40.94</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>72.48999999999999</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>39</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>14746</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
@@ -645,30 +1299,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>成都06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>n78</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>100</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>n78-成都-06</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>42.12</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>69.45999999999999</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>6231</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
@@ -677,30 +1336,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>武汉07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>n78</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>n78-武汉-07</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>57.01</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>14</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>8055</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
@@ -709,30 +1373,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>南京08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>n78</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="n">
         <v>100</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>n78-南京-08</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>82.65000000000001</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>56.83</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>10</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>13449</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>南京</t>
         </is>
@@ -741,30 +1410,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>北京01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>n79</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="n">
         <v>60</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>n79-北京-01</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>35.32</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>82.37</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>43</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>9667</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
@@ -773,30 +1447,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>上海02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>n79</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" t="n">
         <v>60</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>n79-上海-02</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>74.39</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>76.48999999999999</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>39</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>5090</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
@@ -805,30 +1484,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>广州03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>n79</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" t="n">
         <v>60</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>n79-广州-03</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>83.52</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>58.93</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>40</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>10606</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
@@ -837,30 +1521,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>深圳04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>n79</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" t="n">
         <v>60</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>n79-深圳-04</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>75.62</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>70.93000000000001</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>28</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>19918</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
@@ -869,30 +1558,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>杭州05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>n79</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" t="n">
         <v>60</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>n79-杭州-05</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>40.58</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>43.48</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>47</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>8467</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
@@ -901,30 +1595,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>成都06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>n79</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" t="n">
         <v>60</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>n79-成都-06</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>72.52</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>89.26000000000001</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>19</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>4309</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
@@ -933,30 +1632,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>武汉07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>n79</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="C16" t="n">
         <v>60</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>n79-武汉-07</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>50.91</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>62.67</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>28</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>6329</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
@@ -965,30 +1669,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>南京08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>n79</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" t="n">
         <v>60</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>n79-南京-08</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>50.36</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>50.48</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>22</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>23997</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>南京</t>
         </is>
@@ -997,30 +1706,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>北京01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>n41</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="C18" t="n">
         <v>160</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>n41-北京-01</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>81.52</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>43</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>21806</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
@@ -1029,30 +1743,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>上海02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>n41</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="C19" t="n">
         <v>160</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>n41-上海-02</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>39.41</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>76.45999999999999</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>15</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>16147</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
@@ -1061,30 +1780,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>广州03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>n41</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="C20" t="n">
         <v>160</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>n41-广州-03</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>50.87</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>89.48</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>45</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>23549</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
@@ -1093,30 +1817,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>深圳04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>n41</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="C21" t="n">
         <v>160</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>n41-深圳-04</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>60.63</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>74.23</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>8</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>8505</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
@@ -1125,30 +1854,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>杭州05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>n41</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="C22" t="n">
         <v>160</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>n41-杭州-05</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>75.2</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>80.25</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>30</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>9773</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
@@ -1157,30 +1891,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>成都06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>n41</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="C23" t="n">
         <v>160</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>n41-成都-06</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>33.64</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>85.66</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>41</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>24524</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
@@ -1189,30 +1928,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>武汉07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>n41</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="C24" t="n">
         <v>160</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>n41-武汉-07</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>47.31</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>72.77</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>30</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>22064</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
@@ -1221,30 +1965,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>南京08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>n41</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="C25" t="n">
         <v>160</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>n41-南京-08</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>55.24</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>53.24</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>20</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>19394</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>南京</t>
         </is>
@@ -1253,30 +2002,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>北京01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>n28</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="C26" t="n">
         <v>30</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>n28-北京-01</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>59.64</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>77.34999999999999</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>32</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>20121</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
@@ -1285,30 +2039,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>上海02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>n28</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="C27" t="n">
         <v>30</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>n28-上海-02</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>51.97</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>50.97</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>13</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>17696</v>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
@@ -1317,30 +2076,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>广州03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>n28</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="C28" t="n">
         <v>30</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>n28-广州-03</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>57.14</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>77.79000000000001</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>12</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>6008</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
@@ -1349,30 +2113,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>深圳04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>n28</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="C29" t="n">
         <v>30</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>n28-深圳-04</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>64.51000000000001</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>32</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>20543</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
@@ -1381,30 +2150,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>杭州05</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>n28</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="C30" t="n">
         <v>30</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>n28-杭州-05</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>33.49</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>59.08</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>34</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>18338</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
@@ -1413,30 +2187,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>成都06</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>n28</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="C31" t="n">
         <v>30</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>n28-成都-06</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>43.83</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>67.66</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>5</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>23291</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
@@ -1445,30 +2224,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>武汉07</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>n28</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="C32" t="n">
         <v>30</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>n28-武汉-07</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>69.64</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>74.09</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>39</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>9743</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
@@ -1477,30 +2261,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>南京08</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>n28</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="C33" t="n">
         <v>30</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>n28-南京-08</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>72.27</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>57.01</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>23</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>15246</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>南京</t>
         </is>
@@ -1517,38 +2306,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.1"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="2" max="3"/>
+    <col width="10" customWidth="1" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Site ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>小区名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>经度</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>纬度</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>区县</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>覆盖类型</t>
         </is>
@@ -1557,21 +2349,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>北京01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>n78-北京-01</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>115.852364</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>39.652312</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>西城区</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>农村</t>
         </is>
@@ -1580,21 +2377,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>北京02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>n78-北京-02</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>115.9077</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>40.140719</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>朝阳区</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
@@ -1603,21 +2405,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>北京03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>n78-北京-03</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>116.336202</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>39.799319</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>朝阳区</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>郊区</t>
         </is>
@@ -1626,21 +2433,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>北京04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>n78-北京-04</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>115.935057</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>39.936577</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>海淀区</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>郊区</t>
         </is>
@@ -1649,21 +2461,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>北京05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>n78-北京-05</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>115.801671</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>39.861765</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>朝阳区</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
@@ -1672,21 +2489,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>北京06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>n78-北京-06</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>115.869877</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>39.789275</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>西城区</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>市区</t>
         </is>
@@ -1695,21 +2517,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>北京07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>n78-北京-07</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="n">
         <v>116.705399</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>39.655659</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>海淀区</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>郊区</t>
         </is>
@@ -1718,21 +2545,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>北京08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>n78-北京-08</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="n">
         <v>116.590072</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>39.612742</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>西城区</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
@@ -1741,21 +2573,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>上海01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>n79-上海-01</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="n">
         <v>116.065322</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>40.102703</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>东城区</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>农村</t>
         </is>
@@ -1764,21 +2601,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>上海02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>n79-上海-02</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" t="n">
         <v>116.32167</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>39.889777</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>丰台区</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>农村</t>
         </is>
@@ -1787,21 +2629,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>上海03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>n79-上海-03</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" t="n">
         <v>115.812548</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>40.135765</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>丰台区</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
@@ -1810,21 +2657,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>上海04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>n79-上海-04</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" t="n">
         <v>116.484837</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>39.983012</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>丰台区</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
@@ -1833,21 +2685,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>上海05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>n79-上海-05</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" t="n">
         <v>116.320609</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>39.851698</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>丰台区</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>市区</t>
         </is>
@@ -1856,21 +2713,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>上海06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>n79-上海-06</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" t="n">
         <v>116.647342</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>39.987271</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>朝阳区</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
@@ -1879,21 +2741,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>上海07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>n79-上海-07</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="C16" t="n">
         <v>116.458074</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>39.702076</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>东城区</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
@@ -1902,21 +2769,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>上海08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>n79-上海-08</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" t="n">
         <v>116.683917</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>40.033868</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>西城区</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>农村</t>
         </is>
@@ -1925,21 +2797,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>广州01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>n41-广州-01</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="C18" t="n">
         <v>115.816308</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>39.951721</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>东城区</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>市区</t>
         </is>
@@ -1948,21 +2825,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>广州02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>n41-广州-02</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="C19" t="n">
         <v>116.69615</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>40.198532</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>西城区</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>市区</t>
         </is>
@@ -1971,21 +2853,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>广州03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>n41-广州-03</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="C20" t="n">
         <v>116.438801</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>40.195076</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>海淀区</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
@@ -1994,21 +2881,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>广州04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>n41-广州-04</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="C21" t="n">
         <v>116.780675</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>39.692257</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>丰台区</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
@@ -2017,21 +2909,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>广州05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>n41-广州-05</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="C22" t="n">
         <v>116.17859</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>39.876778</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>朝阳区</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>郊区</t>
         </is>
@@ -2040,21 +2937,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>广州06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>n41-广州-06</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="C23" t="n">
         <v>116.25634</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>39.612605</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>东城区</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>农村</t>
         </is>
@@ -2063,21 +2965,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>广州07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>n41-广州-07</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="C24" t="n">
         <v>116.754672</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>39.980561</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>朝阳区</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>市区</t>
         </is>
@@ -2086,21 +2993,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>广州08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>n41-广州-08</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="C25" t="n">
         <v>116.417585</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>39.906192</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>朝阳区</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>市区</t>
         </is>
@@ -2109,21 +3021,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>广州09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>n41-广州-09</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="C26" t="n">
         <v>116.2332</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>39.605137</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>丰台区</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>高速</t>
         </is>
@@ -2132,21 +3049,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>广州10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>n41-广州-10</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="C27" t="n">
         <v>115.873484</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>40.016524</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>西城区</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>市区</t>
         </is>
@@ -2155,21 +3077,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>广州11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>n41-广州-11</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="C28" t="n">
         <v>116.785348</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>39.757524</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>西城区</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>市区</t>
         </is>
@@ -2178,21 +3105,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>广州12</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>n41-广州-12</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="C29" t="n">
         <v>116.550815</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>39.800898</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>东城区</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>市区</t>
         </is>
@@ -2201,21 +3133,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>广州13</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>n41-广州-13</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="C30" t="n">
         <v>116.439128</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>40.181812</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>西城区</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>市区</t>
         </is>
@@ -2224,21 +3161,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>广州14</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>n41-广州-14</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="C31" t="n">
         <v>116.517718</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>40.007431</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>东城区</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>郊区</t>
         </is>
